--- a/SML_PrimaryDataset.xlsx
+++ b/SML_PrimaryDataset.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Win11\Downloads\sml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CAAEDB-79ED-419B-A4F9-4A5650B32069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E508D438-091F-452D-BEC6-7AF7B0B28486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{70B4EEF3-C913-435D-8B45-2A90B9F4FCEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Dictionary" sheetId="1" r:id="rId1"/>
-    <sheet name="Scenarios" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
   <si>
     <t>ResponseID</t>
   </si>
@@ -43,30 +42,9 @@
     <t>ScenarioID</t>
   </si>
   <si>
-    <t>Monday Schedule</t>
-  </si>
-  <si>
-    <t>Tuesday Schedule</t>
-  </si>
-  <si>
-    <t>Wednesday Schedule</t>
-  </si>
-  <si>
-    <t>Thursday Schedule</t>
-  </si>
-  <si>
-    <t>Friday Schedule</t>
-  </si>
-  <si>
-    <t>Saturday Schedule</t>
-  </si>
-  <si>
     <t>Column</t>
   </si>
   <si>
-    <t>SubColumn</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -82,9 +60,6 @@
     <t>System</t>
   </si>
   <si>
-    <t>Pre-Gen</t>
-  </si>
-  <si>
     <t>Commute_Time</t>
   </si>
   <si>
@@ -155,6 +130,27 @@
   </si>
   <si>
     <t>Monday to Saturday</t>
+  </si>
+  <si>
+    <t>Generated</t>
+  </si>
+  <si>
+    <t>Monday Scenario</t>
+  </si>
+  <si>
+    <t>Tuesday Scenario</t>
+  </si>
+  <si>
+    <t>Wednesday Scenario</t>
+  </si>
+  <si>
+    <t>Thursday Scenario</t>
+  </si>
+  <si>
+    <t>Friday Scenario</t>
+  </si>
+  <si>
+    <t>Saturday Scenario</t>
   </si>
 </sst>
 </file>
@@ -172,18 +168,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -200,24 +202,17 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -535,290 +530,287 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40F22A1B-E289-4EC2-BDA3-8F7EE8565500}">
-  <dimension ref="B1:E25"/>
+  <dimension ref="B2:D26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" customWidth="1"/>
-    <col min="5" max="5" width="39.28515625" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D21" t="s">
         <v>31</v>
       </c>
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
         <v>26</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" t="s">
-        <v>18</v>
+      <c r="D26" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -829,15 +821,6 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DC6D90-A74C-44FF-B0ED-F8EE0EC548C5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
